--- a/excel/fused_infer_attention_score.xlsx
+++ b/excel/fused_infer_attention_score.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -536,6 +541,11 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -564,6 +574,11 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -592,6 +607,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -620,6 +640,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -648,6 +673,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -676,6 +706,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -704,6 +739,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -732,6 +772,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -760,6 +805,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -788,6 +838,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -816,6 +871,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -844,6 +904,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -872,6 +937,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -900,6 +966,7 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -928,6 +995,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -956,6 +1024,7 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -984,6 +1053,7 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1012,6 +1082,7 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1040,6 +1111,7 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1068,6 +1140,7 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1096,6 +1169,7 @@
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1124,6 +1198,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1152,6 +1231,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1180,6 +1264,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1208,6 +1297,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1236,6 +1330,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1264,6 +1363,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1292,6 +1396,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1320,6 +1429,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1348,6 +1462,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1376,6 +1495,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1404,6 +1528,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1432,6 +1561,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1460,6 +1594,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1488,6 +1627,7 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1516,6 +1656,7 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1544,6 +1685,7 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1572,6 +1714,7 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1600,6 +1743,7 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1628,6 +1772,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1656,6 +1805,11 @@
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1684,6 +1838,11 @@
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1712,6 +1871,11 @@
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1740,6 +1904,11 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1768,6 +1937,11 @@
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1796,6 +1970,11 @@
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1824,6 +2003,11 @@
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1852,6 +2036,11 @@
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1880,6 +2069,11 @@
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1908,6 +2102,11 @@
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1936,6 +2135,11 @@
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1964,6 +2168,11 @@
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1992,6 +2201,11 @@
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2020,6 +2234,11 @@
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2048,6 +2267,11 @@
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2076,6 +2300,11 @@
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2104,6 +2333,11 @@
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2132,6 +2366,11 @@
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2160,6 +2399,11 @@
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2188,6 +2432,11 @@
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2216,6 +2465,11 @@
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2244,6 +2498,11 @@
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2272,6 +2531,11 @@
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2300,6 +2564,11 @@
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2328,6 +2597,11 @@
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2356,6 +2630,11 @@
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2384,6 +2663,11 @@
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2412,6 +2696,11 @@
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2440,6 +2729,11 @@
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2468,6 +2762,11 @@
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2496,6 +2795,11 @@
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2524,6 +2828,11 @@
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2552,6 +2861,11 @@
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2580,6 +2894,11 @@
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2608,6 +2927,11 @@
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2636,6 +2960,11 @@
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2664,6 +2993,11 @@
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2692,6 +3026,11 @@
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2720,6 +3059,11 @@
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2748,6 +3092,11 @@
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2776,6 +3125,11 @@
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2804,6 +3158,11 @@
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2832,6 +3191,7 @@
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2860,6 +3220,7 @@
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2888,6 +3249,7 @@
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2916,6 +3278,7 @@
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2944,6 +3307,7 @@
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2972,6 +3336,7 @@
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3000,6 +3365,7 @@
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3028,6 +3394,7 @@
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3056,6 +3423,7 @@
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3084,6 +3452,7 @@
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3112,6 +3481,7 @@
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3140,6 +3510,7 @@
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3168,6 +3539,7 @@
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3196,6 +3568,7 @@
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3224,6 +3597,7 @@
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3252,6 +3626,7 @@
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3280,6 +3655,7 @@
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3308,6 +3684,7 @@
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3320,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -3374,6 +3751,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3406,6 +3788,7 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3438,6 +3821,7 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3470,6 +3854,7 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3502,6 +3887,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3534,6 +3920,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3566,6 +3953,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3598,6 +3986,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3626,6 +4015,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3654,6 +4044,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3682,6 +4073,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3710,6 +4102,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3738,6 +4131,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3766,6 +4160,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3798,6 +4193,7 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3826,6 +4222,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3854,6 +4251,7 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3882,6 +4280,7 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3910,6 +4309,7 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3942,6 +4342,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3974,6 +4379,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4006,6 +4416,7 @@
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4038,6 +4449,7 @@
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4070,6 +4482,7 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4102,6 +4515,7 @@
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4134,6 +4548,7 @@
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4166,6 +4581,7 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4198,6 +4614,7 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4230,6 +4647,7 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4262,6 +4680,7 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4294,6 +4713,7 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4326,6 +4746,7 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4358,6 +4779,7 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4390,6 +4812,7 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4422,6 +4845,7 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4454,6 +4878,7 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4486,6 +4911,7 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4518,6 +4944,7 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4550,6 +4977,7 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4582,6 +5010,7 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4614,6 +5043,7 @@
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4646,6 +5076,7 @@
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4678,6 +5109,7 @@
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4710,6 +5142,7 @@
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4742,6 +5175,7 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4774,6 +5208,7 @@
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4806,6 +5241,11 @@
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4838,6 +5278,11 @@
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4870,6 +5315,11 @@
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4902,6 +5352,11 @@
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4930,6 +5385,11 @@
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4962,6 +5422,11 @@
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4994,6 +5459,11 @@
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5026,6 +5496,11 @@
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5058,6 +5533,11 @@
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5090,6 +5570,11 @@
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5122,6 +5607,11 @@
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5154,6 +5644,11 @@
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5186,6 +5681,11 @@
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5218,6 +5718,11 @@
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5250,6 +5755,11 @@
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5282,6 +5792,11 @@
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5314,6 +5829,11 @@
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5346,6 +5866,11 @@
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5378,6 +5903,11 @@
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5410,6 +5940,11 @@
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5438,6 +5973,11 @@
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5470,6 +6010,11 @@
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5502,6 +6047,11 @@
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5534,6 +6084,11 @@
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5566,6 +6121,11 @@
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5598,6 +6158,7 @@
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5630,6 +6191,7 @@
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5662,6 +6224,7 @@
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5694,6 +6257,7 @@
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5726,6 +6290,7 @@
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5758,6 +6323,7 @@
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5786,6 +6352,11 @@
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5814,6 +6385,11 @@
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5846,6 +6422,11 @@
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5878,6 +6459,11 @@
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5910,6 +6496,11 @@
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5942,6 +6533,11 @@
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5970,6 +6566,11 @@
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5998,6 +6599,11 @@
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6030,6 +6636,7 @@
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6062,6 +6669,7 @@
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6094,6 +6702,7 @@
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6126,6 +6735,7 @@
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6154,6 +6764,7 @@
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6186,6 +6797,7 @@
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6218,6 +6830,7 @@
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6250,6 +6863,7 @@
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6282,6 +6896,7 @@
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6314,6 +6929,7 @@
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6346,6 +6962,7 @@
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6378,6 +6995,7 @@
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6410,6 +7028,7 @@
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6438,6 +7057,7 @@
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6470,6 +7090,7 @@
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6502,6 +7123,7 @@
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6534,6 +7156,7 @@
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6566,6 +7189,11 @@
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6598,6 +7226,11 @@
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6610,7 +7243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -6664,6 +7297,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6692,6 +7330,11 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6720,6 +7363,11 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6748,6 +7396,7 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6776,6 +7425,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6804,6 +7454,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6832,6 +7483,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6860,6 +7512,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -6888,6 +7541,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6916,6 +7570,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -6944,6 +7599,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -6972,6 +7628,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7000,6 +7657,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7028,6 +7686,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -7056,6 +7715,7 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7084,6 +7744,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -7112,6 +7773,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -7140,6 +7806,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -7168,6 +7839,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -7196,6 +7872,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -7224,6 +7905,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -7252,6 +7938,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -7280,6 +7971,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -7308,6 +8004,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -7336,6 +8037,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -7364,6 +8070,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -7392,6 +8103,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -7420,6 +8136,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -7448,6 +8169,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -7476,6 +8202,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -7504,6 +8235,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -7532,6 +8268,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -7560,6 +8301,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -7588,6 +8334,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7616,6 +8367,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7644,6 +8400,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7672,6 +8433,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7700,6 +8466,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +8499,11 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7756,6 +8532,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7784,6 +8565,7 @@
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7812,6 +8594,7 @@
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -7840,6 +8623,7 @@
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -7868,6 +8652,7 @@
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -7896,6 +8681,7 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -7924,6 +8710,7 @@
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -7952,6 +8739,7 @@
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -7980,6 +8768,7 @@
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -8008,6 +8797,7 @@
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -8036,6 +8826,7 @@
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -8064,6 +8855,7 @@
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -8092,6 +8884,7 @@
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -8120,6 +8913,7 @@
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -8148,6 +8942,7 @@
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -8176,6 +8971,7 @@
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -8204,6 +9000,7 @@
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -8232,6 +9029,7 @@
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -8260,6 +9058,7 @@
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -8288,6 +9087,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -8316,6 +9116,7 @@
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -8344,6 +9145,7 @@
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -8372,6 +9174,7 @@
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -8400,6 +9203,7 @@
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -8428,6 +9232,7 @@
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -8456,6 +9261,7 @@
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -8484,6 +9290,7 @@
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -8512,6 +9319,7 @@
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -8540,6 +9348,7 @@
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -8568,6 +9377,7 @@
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8596,6 +9406,7 @@
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -8624,6 +9435,7 @@
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -8652,6 +9464,7 @@
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -8680,6 +9493,7 @@
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -8708,6 +9522,7 @@
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -8736,6 +9551,7 @@
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -8764,6 +9580,7 @@
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -8792,6 +9609,7 @@
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -8820,6 +9638,7 @@
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -8848,6 +9667,7 @@
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -8876,6 +9696,7 @@
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -8904,6 +9725,7 @@
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -8932,6 +9754,7 @@
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -8960,6 +9783,7 @@
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -8988,6 +9812,7 @@
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -9016,6 +9841,7 @@
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -9044,6 +9870,7 @@
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -9072,6 +9899,7 @@
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -9100,6 +9928,7 @@
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -9128,6 +9957,11 @@
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -9156,6 +9990,11 @@
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -9184,6 +10023,11 @@
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -9212,6 +10056,11 @@
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -9240,6 +10089,11 @@
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -9268,6 +10122,11 @@
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -9296,6 +10155,11 @@
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -9324,6 +10188,11 @@
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -9352,6 +10221,11 @@
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -9380,6 +10254,11 @@
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -9408,6 +10287,11 @@
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -9436,6 +10320,11 @@
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -9464,6 +10353,11 @@
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -9492,6 +10386,11 @@
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -9520,6 +10419,7 @@
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -9548,6 +10448,7 @@
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -9576,6 +10477,7 @@
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -9604,6 +10506,7 @@
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -9632,6 +10535,7 @@
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -9660,6 +10564,7 @@
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -9688,6 +10593,7 @@
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -9716,6 +10622,7 @@
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -9744,6 +10651,7 @@
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -9772,6 +10680,11 @@
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -9800,6 +10713,11 @@
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -9828,6 +10746,11 @@
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -9856,6 +10779,11 @@
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -9884,6 +10812,11 @@
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -9912,6 +10845,11 @@
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -9940,6 +10878,11 @@
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -9968,6 +10911,11 @@
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -9996,6 +10944,11 @@
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -10024,6 +10977,11 @@
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -10052,6 +11010,11 @@
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -10080,6 +11043,11 @@
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -10108,6 +11076,11 @@
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -10136,6 +11109,11 @@
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -10164,6 +11142,11 @@
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -10192,6 +11175,11 @@
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -10220,6 +11208,11 @@
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -10248,6 +11241,11 @@
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -10276,6 +11274,11 @@
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -10304,6 +11307,11 @@
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -10332,6 +11340,11 @@
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -10360,6 +11373,11 @@
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -10388,6 +11406,11 @@
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -10416,6 +11439,11 @@
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -10444,6 +11472,11 @@
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -10472,6 +11505,11 @@
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -10500,6 +11538,11 @@
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -10528,6 +11571,11 @@
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -10556,6 +11604,11 @@
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -10584,6 +11637,11 @@
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -10612,6 +11670,11 @@
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -10640,6 +11703,11 @@
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -10668,6 +11736,11 @@
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -10696,6 +11769,11 @@
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -10724,6 +11802,11 @@
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -10752,6 +11835,11 @@
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -10780,6 +11868,11 @@
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -10808,6 +11901,11 @@
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -10836,6 +11934,11 @@
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -10864,6 +11967,11 @@
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -10892,6 +12000,11 @@
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -10920,6 +12033,11 @@
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -10948,6 +12066,11 @@
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -10976,6 +12099,11 @@
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -11004,6 +12132,11 @@
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -11032,6 +12165,11 @@
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -11060,6 +12198,7 @@
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -11088,6 +12227,7 @@
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -11116,6 +12256,7 @@
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -11144,6 +12285,7 @@
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -11172,6 +12314,7 @@
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -11200,6 +12343,7 @@
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -11228,6 +12372,7 @@
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -11256,6 +12401,7 @@
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -11284,6 +12430,7 @@
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -11312,6 +12459,7 @@
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -11340,6 +12488,7 @@
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -11368,6 +12517,7 @@
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -11396,6 +12546,7 @@
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -11424,6 +12575,7 @@
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -11452,6 +12604,7 @@
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -11480,6 +12633,7 @@
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -11508,6 +12662,7 @@
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -11536,6 +12691,7 @@
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -11564,6 +12720,7 @@
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -11592,6 +12749,7 @@
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -11620,6 +12778,7 @@
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -11648,6 +12807,7 @@
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -11676,6 +12836,7 @@
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -11704,6 +12865,7 @@
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -11732,6 +12894,7 @@
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -11760,6 +12923,7 @@
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -11788,6 +12952,7 @@
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -11816,6 +12981,7 @@
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -11844,6 +13010,7 @@
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -11872,6 +13039,7 @@
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -11900,6 +13068,7 @@
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -11928,6 +13097,7 @@
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11940,7 +13110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:I190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -11994,6 +13164,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -12022,6 +13197,11 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -12050,6 +13230,11 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -12078,6 +13263,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -12106,6 +13296,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -12134,6 +13329,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -12162,6 +13358,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -12190,6 +13387,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -12218,6 +13416,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -12246,6 +13445,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -12274,6 +13478,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -12302,6 +13511,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -12330,6 +13544,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -12358,6 +13577,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -12386,6 +13610,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -12414,6 +13643,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -12442,6 +13676,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -12470,6 +13709,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -12498,6 +13742,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -12526,6 +13775,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -12554,6 +13808,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -12582,6 +13841,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -12610,6 +13874,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -12638,6 +13907,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -12666,6 +13940,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -12694,6 +13973,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -12722,6 +14006,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -12750,6 +14039,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -12778,6 +14072,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -12806,6 +14105,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -12834,6 +14138,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -12862,6 +14171,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -12890,6 +14204,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -12918,6 +14237,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -12946,6 +14270,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -12974,6 +14303,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -13002,6 +14336,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -13030,6 +14369,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -13058,6 +14402,11 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -13086,6 +14435,7 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -13114,6 +14464,7 @@
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -13142,6 +14493,7 @@
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -13170,6 +14522,7 @@
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -13198,6 +14551,7 @@
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -13226,6 +14580,7 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -13254,6 +14609,7 @@
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -13282,6 +14638,7 @@
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -13310,6 +14667,7 @@
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -13338,6 +14696,7 @@
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -13366,6 +14725,7 @@
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -13394,6 +14754,7 @@
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -13422,6 +14783,7 @@
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -13450,6 +14812,7 @@
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -13478,6 +14841,7 @@
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -13506,6 +14870,7 @@
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -13534,6 +14899,7 @@
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -13562,6 +14928,7 @@
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -13590,6 +14957,7 @@
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -13618,6 +14986,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -13646,6 +15015,7 @@
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -13674,6 +15044,7 @@
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -13702,6 +15073,7 @@
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -13730,6 +15102,7 @@
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -13758,6 +15131,7 @@
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -13786,6 +15160,7 @@
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -13814,6 +15189,7 @@
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -13842,6 +15218,7 @@
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -13870,6 +15247,7 @@
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13898,6 +15276,7 @@
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13926,6 +15305,7 @@
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13954,6 +15334,7 @@
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13982,6 +15363,7 @@
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -14010,6 +15392,7 @@
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -14038,6 +15421,7 @@
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14066,6 +15450,7 @@
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14094,6 +15479,7 @@
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14122,6 +15508,7 @@
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14150,6 +15537,7 @@
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14178,6 +15566,7 @@
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14206,6 +15595,11 @@
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14234,6 +15628,11 @@
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14262,6 +15661,11 @@
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14290,6 +15694,11 @@
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14318,6 +15727,11 @@
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -14346,6 +15760,11 @@
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -14374,6 +15793,11 @@
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -14402,6 +15826,11 @@
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -14430,6 +15859,11 @@
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -14458,6 +15892,11 @@
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -14486,6 +15925,11 @@
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -14514,6 +15958,11 @@
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -14542,6 +15991,11 @@
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -14570,6 +16024,11 @@
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -14598,6 +16057,7 @@
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -14626,6 +16086,11 @@
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -14654,6 +16119,11 @@
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -14682,6 +16152,11 @@
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -14710,6 +16185,11 @@
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -14738,6 +16218,11 @@
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -14766,6 +16251,11 @@
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -14794,6 +16284,11 @@
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -14822,6 +16317,11 @@
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -14850,6 +16350,11 @@
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -14878,6 +16383,11 @@
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -14906,6 +16416,11 @@
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -14934,6 +16449,11 @@
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -14962,6 +16482,11 @@
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -14990,6 +16515,11 @@
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -15018,6 +16548,11 @@
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -15046,6 +16581,11 @@
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -15074,6 +16614,11 @@
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -15102,6 +16647,11 @@
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -15130,6 +16680,11 @@
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -15158,6 +16713,11 @@
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -15186,6 +16746,11 @@
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -15214,6 +16779,11 @@
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -15242,6 +16812,11 @@
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -15270,6 +16845,11 @@
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -15298,6 +16878,11 @@
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -15326,6 +16911,11 @@
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -15354,6 +16944,11 @@
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -15382,6 +16977,11 @@
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -15410,6 +17010,11 @@
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -15438,6 +17043,11 @@
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -15466,6 +17076,11 @@
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -15494,6 +17109,11 @@
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -15522,6 +17142,11 @@
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -15550,6 +17175,11 @@
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -15578,6 +17208,11 @@
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -15606,6 +17241,11 @@
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -15634,6 +17274,11 @@
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -15662,6 +17307,11 @@
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -15690,6 +17340,7 @@
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -15718,6 +17369,7 @@
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -15746,6 +17398,7 @@
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -15774,6 +17427,7 @@
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -15802,6 +17456,7 @@
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -15830,6 +17485,7 @@
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -15858,6 +17514,7 @@
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -15886,6 +17543,7 @@
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -15914,6 +17572,7 @@
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -15942,6 +17601,7 @@
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -15970,6 +17630,7 @@
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -15998,6 +17659,7 @@
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -16026,6 +17688,7 @@
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -16054,6 +17717,7 @@
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -16082,6 +17746,7 @@
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -16110,6 +17775,7 @@
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -16138,6 +17804,7 @@
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -16166,6 +17833,7 @@
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -16194,6 +17862,7 @@
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -16222,6 +17891,7 @@
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -16250,6 +17920,7 @@
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -16278,6 +17949,7 @@
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -16306,6 +17978,7 @@
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -16334,6 +18007,7 @@
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -16362,6 +18036,7 @@
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -16390,6 +18065,7 @@
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -16418,6 +18094,7 @@
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -16446,6 +18123,7 @@
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -16474,6 +18152,7 @@
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -16502,6 +18181,7 @@
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -16530,6 +18210,7 @@
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -16558,6 +18239,7 @@
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -16586,6 +18268,7 @@
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -16614,6 +18297,7 @@
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -16642,6 +18326,7 @@
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -16670,6 +18355,7 @@
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -16698,6 +18384,7 @@
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -16726,6 +18413,7 @@
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -16754,6 +18442,7 @@
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -16782,6 +18471,7 @@
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -16810,6 +18500,7 @@
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -16838,6 +18529,7 @@
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -16866,6 +18558,7 @@
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -16894,6 +18587,7 @@
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -16922,6 +18616,7 @@
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -16950,6 +18645,7 @@
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -16978,6 +18674,7 @@
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -17006,6 +18703,7 @@
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -17034,6 +18732,7 @@
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -17062,6 +18761,7 @@
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -17090,6 +18790,7 @@
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -17118,6 +18819,7 @@
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -17146,6 +18848,7 @@
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -17174,6 +18877,7 @@
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -17202,6 +18906,7 @@
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -17230,6 +18935,7 @@
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -17258,6 +18964,7 @@
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -17286,6 +18993,7 @@
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17298,7 +19006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -17352,6 +19060,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -17380,6 +19093,7 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -17408,6 +19122,7 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -17436,6 +19151,7 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -17464,6 +19180,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -17492,6 +19209,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -17520,6 +19238,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -17548,6 +19267,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -17576,6 +19296,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -17604,6 +19325,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -17632,6 +19358,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -17660,6 +19391,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -17688,6 +19424,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -17716,6 +19457,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -17744,6 +19490,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -17772,6 +19523,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -17800,6 +19556,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -17828,6 +19589,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -17856,6 +19622,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -17884,6 +19655,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -17912,6 +19688,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -17940,6 +19721,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -17968,6 +19754,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -17996,6 +19787,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -18024,6 +19820,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -18052,6 +19853,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -18080,6 +19886,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -18108,6 +19919,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -18136,6 +19952,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -18164,6 +19985,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -18192,6 +20018,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -18220,6 +20051,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -18248,6 +20084,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -18276,6 +20117,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -18304,6 +20150,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -18332,6 +20183,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -18360,6 +20216,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -18388,6 +20249,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -18416,6 +20282,11 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -18444,6 +20315,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -18472,6 +20348,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -18500,6 +20381,11 @@
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -18528,6 +20414,11 @@
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -18556,6 +20447,11 @@
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -18584,6 +20480,11 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -18612,6 +20513,11 @@
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -18640,6 +20546,11 @@
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -18668,6 +20579,11 @@
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -18696,6 +20612,11 @@
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -18724,6 +20645,11 @@
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -18752,6 +20678,11 @@
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -18780,6 +20711,11 @@
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -18808,6 +20744,11 @@
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -18836,6 +20777,11 @@
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -18864,6 +20810,11 @@
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -18892,6 +20843,11 @@
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -18920,6 +20876,11 @@
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -18948,6 +20909,11 @@
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -18976,6 +20942,11 @@
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -19004,6 +20975,11 @@
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -19032,6 +21008,11 @@
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -19060,6 +21041,11 @@
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -19088,6 +21074,11 @@
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -19116,6 +21107,11 @@
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -19144,6 +21140,11 @@
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -19172,6 +21173,11 @@
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -19200,6 +21206,11 @@
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -19228,6 +21239,7 @@
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -19256,6 +21268,7 @@
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -19284,6 +21297,7 @@
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -19312,6 +21326,7 @@
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -19340,6 +21355,7 @@
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -19368,6 +21384,7 @@
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -19396,6 +21413,7 @@
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -19424,6 +21442,7 @@
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -19452,6 +21471,7 @@
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -19480,6 +21500,7 @@
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -19508,6 +21529,7 @@
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -19536,6 +21558,7 @@
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -19564,6 +21587,7 @@
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -19592,6 +21616,7 @@
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -19620,6 +21645,7 @@
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -19648,6 +21674,7 @@
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -19676,6 +21703,7 @@
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -19704,6 +21732,7 @@
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -19732,6 +21761,11 @@
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -19760,6 +21794,11 @@
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -19788,6 +21827,11 @@
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -19816,6 +21860,11 @@
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -19844,6 +21893,11 @@
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -19872,6 +21926,11 @@
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -19900,6 +21959,11 @@
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -19928,6 +21992,11 @@
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -19956,6 +22025,7 @@
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -19984,6 +22054,7 @@
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -20012,6 +22083,7 @@
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -20040,6 +22112,7 @@
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -20068,6 +22141,7 @@
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -20096,6 +22170,7 @@
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -20124,6 +22199,7 @@
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -20152,6 +22228,7 @@
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -20180,6 +22257,7 @@
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -20208,6 +22286,7 @@
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -20236,6 +22315,7 @@
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -20264,6 +22344,7 @@
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -20292,6 +22373,7 @@
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -20320,6 +22402,7 @@
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -20348,6 +22431,7 @@
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -20376,6 +22460,7 @@
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -20404,6 +22489,11 @@
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -20432,6 +22522,11 @@
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -20460,6 +22555,11 @@
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -20488,6 +22588,11 @@
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -20516,6 +22621,11 @@
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -20544,6 +22654,11 @@
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -20572,6 +22687,11 @@
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -20600,6 +22720,11 @@
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -20628,6 +22753,11 @@
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -20656,6 +22786,11 @@
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -20684,6 +22819,11 @@
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -20712,6 +22852,11 @@
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -20740,6 +22885,11 @@
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -20768,6 +22918,11 @@
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -20796,6 +22951,11 @@
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -20824,6 +22984,11 @@
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -20852,6 +23017,11 @@
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -20880,6 +23050,11 @@
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -20908,6 +23083,11 @@
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -20936,6 +23116,11 @@
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -20964,6 +23149,11 @@
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -20992,6 +23182,11 @@
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -21020,6 +23215,11 @@
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -21048,6 +23248,11 @@
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -21076,6 +23281,11 @@
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -21104,6 +23314,11 @@
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -21132,6 +23347,11 @@
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -21160,6 +23380,11 @@
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -21188,6 +23413,11 @@
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -21216,6 +23446,11 @@
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -21244,6 +23479,11 @@
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -21272,6 +23512,11 @@
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -21300,6 +23545,11 @@
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -21328,6 +23578,11 @@
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -21356,6 +23611,11 @@
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -21384,6 +23644,11 @@
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -21412,6 +23677,11 @@
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -21440,6 +23710,11 @@
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -21468,6 +23743,11 @@
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -21496,6 +23776,11 @@
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -21524,6 +23809,11 @@
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -21552,6 +23842,11 @@
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -21580,6 +23875,11 @@
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -21608,6 +23908,11 @@
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -21636,6 +23941,11 @@
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -21664,6 +23974,11 @@
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -21692,6 +24007,11 @@
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -21720,6 +24040,11 @@
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -21748,6 +24073,11 @@
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -21776,6 +24106,11 @@
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -21804,6 +24139,11 @@
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -21832,6 +24172,11 @@
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -21860,6 +24205,11 @@
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -21888,6 +24238,11 @@
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -21916,6 +24271,11 @@
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -21944,6 +24304,11 @@
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -21972,6 +24337,11 @@
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -22000,6 +24370,11 @@
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -22028,6 +24403,11 @@
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -22056,6 +24436,11 @@
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -22084,6 +24469,11 @@
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -22112,6 +24502,11 @@
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -22140,6 +24535,11 @@
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -22168,6 +24568,11 @@
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -22196,6 +24601,11 @@
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -22224,6 +24634,7 @@
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -22252,6 +24663,7 @@
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -22280,6 +24692,7 @@
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -22308,6 +24721,7 @@
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -22336,6 +24750,7 @@
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -22364,6 +24779,7 @@
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -22392,6 +24808,7 @@
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -22420,6 +24837,7 @@
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -22448,6 +24866,7 @@
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -22476,6 +24895,7 @@
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -22504,6 +24924,7 @@
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -22532,6 +24953,7 @@
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -22560,6 +24982,7 @@
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -22588,6 +25011,7 @@
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -22616,6 +25040,7 @@
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -22644,6 +25069,7 @@
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -22672,6 +25098,7 @@
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -22700,6 +25127,7 @@
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -22728,6 +25156,7 @@
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -22756,6 +25185,7 @@
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -22784,6 +25214,7 @@
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -22812,6 +25243,7 @@
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -22840,6 +25272,7 @@
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -22868,6 +25301,7 @@
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -22896,6 +25330,7 @@
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -22924,6 +25359,7 @@
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -22952,6 +25388,7 @@
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -22980,6 +25417,7 @@
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -23008,6 +25446,7 @@
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -23036,6 +25475,7 @@
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -23064,6 +25504,11 @@
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -23092,6 +25537,11 @@
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23104,7 +25554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -23158,6 +25608,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -23186,6 +25641,7 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -23214,6 +25670,7 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -23242,6 +25699,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -23270,6 +25732,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -23298,6 +25765,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -23326,6 +25798,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -23354,6 +25831,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -23382,6 +25864,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -23410,6 +25893,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -23438,6 +25922,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -23466,6 +25951,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -23494,6 +25980,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -23522,6 +26013,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -23550,6 +26046,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -23578,6 +26079,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -23606,6 +26112,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -23634,6 +26145,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -23662,6 +26178,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -23690,6 +26211,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -23718,6 +26244,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -23746,6 +26277,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -23774,6 +26310,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -23802,6 +26343,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -23830,6 +26376,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -23858,6 +26409,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -23886,6 +26442,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -23914,6 +26475,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -23942,6 +26508,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -23970,6 +26541,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -23998,6 +26574,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -24026,6 +26607,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -24054,6 +26640,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -24082,6 +26673,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -24110,6 +26706,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -24138,6 +26739,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -24166,6 +26772,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -24194,6 +26805,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -24222,6 +26838,11 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -24250,6 +26871,7 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24262,7 +26884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -24316,6 +26938,11 @@
           <t>替换</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -24344,6 +26971,7 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -24372,6 +27000,7 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -24400,6 +27029,7 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -24428,6 +27058,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -24456,6 +27087,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -24484,6 +27116,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -24512,6 +27145,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -24540,6 +27174,7 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -24568,6 +27203,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -24596,6 +27232,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -24624,6 +27261,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -24652,6 +27290,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -24680,6 +27319,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -24708,6 +27352,7 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -24736,6 +27381,7 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -24764,6 +27410,7 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -24792,6 +27439,7 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -24820,6 +27468,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -24848,6 +27501,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -24876,6 +27534,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -24904,6 +27567,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -24932,6 +27600,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -24960,6 +27633,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -24988,6 +27666,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -25016,6 +27699,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -25044,6 +27732,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>transformer-3@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -25072,6 +27765,7 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -25100,6 +27794,7 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -25128,6 +27823,7 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -25156,6 +27852,7 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -25184,6 +27881,7 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -25212,6 +27910,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -25240,6 +27943,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -25268,6 +27976,7 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -25296,6 +28005,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -25324,6 +28038,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -25352,6 +28071,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -25380,6 +28104,11 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -25408,6 +28137,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -25436,6 +28170,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -25464,6 +28203,11 @@
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -25492,6 +28236,11 @@
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -25520,6 +28269,11 @@
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -25548,6 +28302,11 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -25576,6 +28335,11 @@
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -25604,6 +28368,11 @@
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -25632,6 +28401,11 @@
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -25660,6 +28434,11 @@
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -25688,6 +28467,11 @@
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -25716,6 +28500,11 @@
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -25744,6 +28533,7 @@
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -25772,6 +28562,7 @@
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -25800,6 +28591,7 @@
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -25828,6 +28620,7 @@
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -25856,6 +28649,7 @@
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -25884,6 +28678,7 @@
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -25912,6 +28707,7 @@
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -25940,6 +28736,7 @@
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -25968,6 +28765,7 @@
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -25996,6 +28794,7 @@
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -26024,6 +28823,11 @@
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -26052,6 +28856,11 @@
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -26080,6 +28889,11 @@
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -26108,6 +28922,11 @@
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -26136,6 +28955,11 @@
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -26164,6 +28988,11 @@
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -26192,6 +29021,11 @@
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -26220,6 +29054,11 @@
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -26248,6 +29087,11 @@
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -26276,6 +29120,11 @@
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -26304,6 +29153,11 @@
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -26332,6 +29186,11 @@
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -26360,6 +29219,11 @@
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -26388,6 +29252,11 @@
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -26416,6 +29285,11 @@
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -26444,6 +29318,11 @@
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -26472,6 +29351,11 @@
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -26500,6 +29384,11 @@
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -26528,6 +29417,11 @@
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>transformer-5@ops-transformer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
